--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.97134792290132</v>
+        <v>2.107844037471465</v>
       </c>
       <c r="D2" t="n">
-        <v>25.65084445839093</v>
+        <v>4.168262224488527</v>
       </c>
       <c r="E2" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F2" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.831241943619399</v>
+        <v>1.272576815838152</v>
       </c>
       <c r="D3" t="n">
-        <v>31.02306985523734</v>
+        <v>5.041248851476068</v>
       </c>
       <c r="E3" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F3" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.649791025832362</v>
+        <v>1.568091041697759</v>
       </c>
       <c r="D4" t="n">
-        <v>10.20258524287841</v>
+        <v>1.657920101967742</v>
       </c>
       <c r="E4" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F4" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.19040402875067</v>
+        <v>2.630940654671984</v>
       </c>
       <c r="D5" t="n">
-        <v>15.64031261727117</v>
+        <v>2.541550800306565</v>
       </c>
       <c r="E5" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F5" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.247508136943594</v>
+        <v>1.340220072253334</v>
       </c>
       <c r="D6" t="n">
-        <v>8.077078498597446</v>
+        <v>1.312525256022085</v>
       </c>
       <c r="E6" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F6" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.173466556826147</v>
+        <v>1.328188315484249</v>
       </c>
       <c r="D7" t="n">
-        <v>14.96254506816796</v>
+        <v>2.431413573577293</v>
       </c>
       <c r="E7" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F7" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.790329695269428</v>
+        <v>1.428428575481282</v>
       </c>
       <c r="D8" t="n">
-        <v>21.85886994235035</v>
+        <v>3.552066365631931</v>
       </c>
       <c r="E8" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F8" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.676462121975468</v>
+        <v>0.9224250948210135</v>
       </c>
       <c r="D9" t="n">
-        <v>19.24880727818358</v>
+        <v>3.127931182704832</v>
       </c>
       <c r="E9" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F9" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.932448695990046</v>
+        <v>0.8015229130983825</v>
       </c>
       <c r="D10" t="n">
-        <v>28.43539406292749</v>
+        <v>4.620751535225717</v>
       </c>
       <c r="E10" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F10" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.27360568009291</v>
+        <v>2.969460923015097</v>
       </c>
       <c r="D11" t="n">
-        <v>23.44322858855658</v>
+        <v>3.809524645640443</v>
       </c>
       <c r="E11" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F11" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.07948925263712</v>
+        <v>2.125417003553533</v>
       </c>
       <c r="D12" t="n">
-        <v>15.75053757384227</v>
+        <v>2.559462355749369</v>
       </c>
       <c r="E12" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F12" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.200076520633267</v>
+        <v>1.332512434602906</v>
       </c>
       <c r="D13" t="n">
-        <v>11.94831582692362</v>
+        <v>1.941601321875088</v>
       </c>
       <c r="E13" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F13" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.74372752449115</v>
+        <v>2.070855722729813</v>
       </c>
       <c r="D14" t="n">
-        <v>10.87781000069358</v>
+        <v>1.767644125112707</v>
       </c>
       <c r="E14" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F14" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>16.92852831924821</v>
+        <v>2.750885851877834</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7182914836465</v>
+        <v>1.741722366092557</v>
       </c>
       <c r="E15" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F15" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>21.63773882800879</v>
+        <v>3.516132559551428</v>
       </c>
       <c r="D16" t="n">
-        <v>18.84754052161653</v>
+        <v>3.062725334762686</v>
       </c>
       <c r="E16" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F16" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.57332728842988</v>
+        <v>4.805665684369855</v>
       </c>
       <c r="D17" t="n">
-        <v>27.13562549981606</v>
+        <v>4.409539143720109</v>
       </c>
       <c r="E17" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F17" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.76313910262364</v>
+        <v>3.536510104176342</v>
       </c>
       <c r="D18" t="n">
-        <v>3.072083409286953</v>
+        <v>0.4992135540091299</v>
       </c>
       <c r="E18" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F18" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>15.84616153345366</v>
+        <v>2.57500124918622</v>
       </c>
       <c r="D19" t="n">
-        <v>10.97051111813892</v>
+        <v>1.782708056697575</v>
       </c>
       <c r="E19" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F19" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>24.32833233048286</v>
+        <v>3.953354003703465</v>
       </c>
       <c r="D20" t="n">
-        <v>19.68146800402971</v>
+        <v>3.198238550654827</v>
       </c>
       <c r="E20" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F20" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>21.05316558398094</v>
+        <v>3.421139407396903</v>
       </c>
       <c r="D21" t="n">
-        <v>22.02508442255924</v>
+        <v>3.579076218665876</v>
       </c>
       <c r="E21" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F21" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>6.330615309543687</v>
+        <v>1.028724987800849</v>
       </c>
       <c r="D22" t="n">
-        <v>7.562646992630783</v>
+        <v>1.228930136302502</v>
       </c>
       <c r="E22" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F22" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>9.088885736245405</v>
+        <v>1.476943932139879</v>
       </c>
       <c r="D23" t="n">
-        <v>8.913803196089171</v>
+        <v>1.44849301936449</v>
       </c>
       <c r="E23" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F23" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>7.065876593492994</v>
+        <v>1.148204946442612</v>
       </c>
       <c r="D24" t="n">
-        <v>8.815462929530408</v>
+        <v>1.432512726048691</v>
       </c>
       <c r="E24" t="n">
-        <v>6.644155589174463</v>
+        <v>1.07967528324085</v>
       </c>
       <c r="F24" t="n">
-        <v>7.481336196825522</v>
+        <v>1.215717131984148</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
